--- a/data/Base_Transporte.xlsx
+++ b/data/Base_Transporte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin/Documents/Personal/Cursos_UNAM/Series-Tiempo/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB0EF40-C5CF-DB49-A861-9D69E632D137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4029A4C-5F7C-1B4A-8CC4-2FB69EA35DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34380" yWindow="500" windowWidth="16000" windowHeight="18880" xr2:uid="{010589B2-5E98-1D40-AEE0-AA1A110D1180}"/>
+    <workbookView xWindow="12980" yWindow="660" windowWidth="16000" windowHeight="18880" xr2:uid="{010589B2-5E98-1D40-AEE0-AA1A110D1180}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E033B569-E481-7947-93CD-4A9A959244F1}">
-  <dimension ref="A1:F307"/>
+  <dimension ref="A1:F318"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -6201,13 +6201,13 @@
         <v>45292</v>
       </c>
       <c r="B290" s="1">
-        <v>4750992</v>
+        <v>4756496</v>
       </c>
       <c r="C290" s="1">
-        <v>2709727</v>
+        <v>2714574</v>
       </c>
       <c r="D290" s="1">
-        <v>32833</v>
+        <v>32834</v>
       </c>
       <c r="E290" s="1">
         <v>19147</v>
@@ -6221,10 +6221,10 @@
         <v>45323</v>
       </c>
       <c r="B291" s="1">
-        <v>4322342</v>
+        <v>4327042</v>
       </c>
       <c r="C291" s="1">
-        <v>2565792</v>
+        <v>2568796</v>
       </c>
       <c r="D291" s="1">
         <v>29949</v>
@@ -6241,10 +6241,10 @@
         <v>45352</v>
       </c>
       <c r="B292" s="1">
-        <v>4790485</v>
+        <v>4796255</v>
       </c>
       <c r="C292" s="1">
-        <v>2858810</v>
+        <v>2865372</v>
       </c>
       <c r="D292" s="1">
         <v>32478</v>
@@ -6261,10 +6261,10 @@
         <v>45383</v>
       </c>
       <c r="B293" s="1">
-        <v>4923234</v>
+        <v>4924133</v>
       </c>
       <c r="C293" s="1">
-        <v>2358433</v>
+        <v>2360629</v>
       </c>
       <c r="D293" s="1">
         <v>34798</v>
@@ -6281,10 +6281,10 @@
         <v>45413</v>
       </c>
       <c r="B294" s="1">
-        <v>5166797</v>
+        <v>5168692</v>
       </c>
       <c r="C294" s="1">
-        <v>2267937</v>
+        <v>2271781</v>
       </c>
       <c r="D294" s="1">
         <v>36265</v>
@@ -6361,16 +6361,16 @@
         <v>45536</v>
       </c>
       <c r="B298" s="1">
-        <v>4806392</v>
+        <v>4806489</v>
       </c>
       <c r="C298" s="1">
-        <v>1790672</v>
+        <v>1790786</v>
       </c>
       <c r="D298" s="1">
-        <v>33501</v>
+        <v>33502</v>
       </c>
       <c r="E298" s="1">
-        <v>16390</v>
+        <v>12824</v>
       </c>
       <c r="F298" s="1">
         <v>99.794983000000002</v>
@@ -6401,16 +6401,16 @@
         <v>45597</v>
       </c>
       <c r="B300" s="1">
-        <v>5110702</v>
+        <v>5110827</v>
       </c>
       <c r="C300" s="1">
         <v>2511002</v>
       </c>
       <c r="D300" s="1">
-        <v>34877</v>
+        <v>34947</v>
       </c>
       <c r="E300" s="1">
-        <v>16937</v>
+        <v>16969</v>
       </c>
       <c r="F300" s="1">
         <v>103.368953</v>
@@ -6554,6 +6554,226 @@
       </c>
       <c r="F307" s="1">
         <v>100.15273000000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A308" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B308">
+        <v>5614840</v>
+      </c>
+      <c r="C308">
+        <v>2582438</v>
+      </c>
+      <c r="D308">
+        <v>37207</v>
+      </c>
+      <c r="E308">
+        <v>17826</v>
+      </c>
+      <c r="F308">
+        <v>103.165584</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A309" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B309">
+        <v>5542718</v>
+      </c>
+      <c r="C309">
+        <v>2248212</v>
+      </c>
+      <c r="D309">
+        <v>36544</v>
+      </c>
+      <c r="E309">
+        <v>15789</v>
+      </c>
+      <c r="F309">
+        <v>105.75252500000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A310" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B310">
+        <v>4884688</v>
+      </c>
+      <c r="C310">
+        <v>1805016</v>
+      </c>
+      <c r="D310">
+        <v>35097</v>
+      </c>
+      <c r="E310">
+        <v>13037</v>
+      </c>
+      <c r="F310">
+        <v>105.27370500000001</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A311" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B311">
+        <v>5236656</v>
+      </c>
+      <c r="C311">
+        <v>2162990</v>
+      </c>
+      <c r="D311">
+        <v>35445</v>
+      </c>
+      <c r="E311">
+        <v>14465</v>
+      </c>
+      <c r="F311">
+        <v>115.57213900000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A312" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B312">
+        <v>5004045</v>
+      </c>
+      <c r="C312">
+        <v>2308745</v>
+      </c>
+      <c r="D312">
+        <v>35516</v>
+      </c>
+      <c r="E312">
+        <v>16810</v>
+      </c>
+      <c r="F312">
+        <v>106.83618300000001</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A313" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B313">
+        <v>5510046</v>
+      </c>
+      <c r="C313">
+        <v>3163463</v>
+      </c>
+      <c r="D313">
+        <v>37860</v>
+      </c>
+      <c r="E313">
+        <v>20686</v>
+      </c>
+      <c r="F313">
+        <v>107.239178</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A314" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B314">
+        <v>5146555</v>
+      </c>
+      <c r="C314">
+        <v>2418658</v>
+      </c>
+      <c r="D314">
+        <v>35653</v>
+      </c>
+      <c r="E314">
+        <v>17133</v>
+      </c>
+      <c r="F314">
+        <v>100.789164</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A315" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B315">
+        <v>4363046</v>
+      </c>
+      <c r="C315">
+        <v>2475706</v>
+      </c>
+      <c r="D315">
+        <v>31073</v>
+      </c>
+      <c r="E315">
+        <v>17575</v>
+      </c>
+      <c r="F315">
+        <v>98.627598000000006</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A316" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B316">
+        <v>4948009</v>
+      </c>
+      <c r="C316">
+        <v>2824687</v>
+      </c>
+      <c r="D316">
+        <v>33872</v>
+      </c>
+      <c r="E316">
+        <v>19990</v>
+      </c>
+      <c r="F316">
+        <v>107.426886</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A317" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B317">
+        <v>4784621</v>
+      </c>
+      <c r="C317">
+        <v>2710500</v>
+      </c>
+      <c r="D317">
+        <v>33629</v>
+      </c>
+      <c r="E317">
+        <v>19167</v>
+      </c>
+      <c r="F317">
+        <v>100.380478</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A318" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B318">
+        <v>5244179</v>
+      </c>
+      <c r="C318">
+        <v>2218860.3333333335</v>
+      </c>
+      <c r="D318">
+        <v>36879</v>
+      </c>
+      <c r="E318">
+        <v>15781</v>
+      </c>
+      <c r="F318">
+        <v>103.936258</v>
       </c>
     </row>
   </sheetData>
